--- a/outputs/TAS_negative_prices.xlsx
+++ b/outputs/TAS_negative_prices.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J85"/>
+  <dimension ref="A1:J86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3372,6 +3372,40 @@
         <v>0</v>
       </c>
     </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3383,7 +3417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J85"/>
+  <dimension ref="A1:J86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6306,8 +6340,42 @@
         <v>0</v>
       </c>
     </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B85">
+  <conditionalFormatting sqref="B2:B86">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -6319,7 +6387,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C85">
+  <conditionalFormatting sqref="C2:C86">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -6331,7 +6399,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D85">
+  <conditionalFormatting sqref="D2:D86">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -6343,7 +6411,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E85">
+  <conditionalFormatting sqref="E2:E86">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -6355,7 +6423,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F85">
+  <conditionalFormatting sqref="F2:F86">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -6367,7 +6435,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G85">
+  <conditionalFormatting sqref="G2:G86">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
@@ -6379,7 +6447,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H85">
+  <conditionalFormatting sqref="H2:H86">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
@@ -6391,7 +6459,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I85">
+  <conditionalFormatting sqref="I2:I86">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
@@ -6403,7 +6471,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J85">
+  <conditionalFormatting sqref="J2:J86">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
@@ -6425,7 +6493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K85"/>
+  <dimension ref="A1:K86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9606,6 +9674,43 @@
         <v>0</v>
       </c>
     </row>
+    <row r="86">
+      <c r="A86" s="5" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="B86" s="5" t="n">
+        <v>2976</v>
+      </c>
+      <c r="C86" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D86" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E86" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K86" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/TAS_negative_prices.xlsx
+++ b/outputs/TAS_negative_prices.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J86"/>
+  <dimension ref="A1:J87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3406,6 +3406,40 @@
         <v>0</v>
       </c>
     </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3417,7 +3451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J86"/>
+  <dimension ref="A1:J87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6374,8 +6408,42 @@
         <v>0</v>
       </c>
     </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B86">
+  <conditionalFormatting sqref="B2:B87">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -6387,7 +6455,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C86">
+  <conditionalFormatting sqref="C2:C87">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -6399,7 +6467,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D86">
+  <conditionalFormatting sqref="D2:D87">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -6411,7 +6479,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E86">
+  <conditionalFormatting sqref="E2:E87">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -6423,7 +6491,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F86">
+  <conditionalFormatting sqref="F2:F87">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -6435,7 +6503,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G86">
+  <conditionalFormatting sqref="G2:G87">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
@@ -6447,7 +6515,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H86">
+  <conditionalFormatting sqref="H2:H87">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
@@ -6459,7 +6527,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I86">
+  <conditionalFormatting sqref="I2:I87">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
@@ -6471,7 +6539,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J86">
+  <conditionalFormatting sqref="J2:J87">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
@@ -6493,7 +6561,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K86"/>
+  <dimension ref="A1:K87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9711,6 +9779,43 @@
         <v>0</v>
       </c>
     </row>
+    <row r="87">
+      <c r="A87" s="5" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="B87" s="5" t="n">
+        <v>2880</v>
+      </c>
+      <c r="C87" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D87" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E87" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K87" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/TAS_negative_prices.xlsx
+++ b/outputs/TAS_negative_prices.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Percentages" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Heatmap" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Audit" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Percentages" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Heatmap" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audit" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>0</v>
@@ -761,25 +761,25 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>4.64</v>
+        <v>4.5</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.97</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>0.84</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="I9" s="3" t="n">
         <v>0.03</v>
@@ -795,31 +795,31 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.87</v>
+        <v>0.91</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.84</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.74</v>
+        <v>0.77</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.74</v>
+        <v>0.77</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.17</v>
+        <v>0.2</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.17</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="11">
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>0.6</v>
@@ -931,25 +931,25 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>6.75</v>
+        <v>6.38</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.2</v>
+        <v>0.24</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.13</v>
+        <v>0.17</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>0</v>
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.67</v>
+        <v>0.47</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>0.2</v>
@@ -1101,16 +1101,16 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>8.17</v>
+        <v>8.06</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>4.17</v>
+        <v>4.13</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>3.63</v>
+        <v>3.6</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="F19" s="3" t="n">
         <v>2.35</v>
@@ -1169,16 +1169,16 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>7.49</v>
+        <v>7.33</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>5.01</v>
+        <v>5.04</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>4.91</v>
+        <v>4.94</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>4.54</v>
+        <v>4.57</v>
       </c>
       <c r="F21" s="3" t="n">
         <v>2.62</v>
@@ -1305,7 +1305,7 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>6.01</v>
+        <v>5.94</v>
       </c>
       <c r="C25" s="3" t="n">
         <v>0.9</v>
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="C26" s="3" t="n">
         <v>0.3</v>
@@ -1373,16 +1373,16 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>2.71</v>
+        <v>2.67</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>0.17</v>
@@ -1407,16 +1407,16 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>12.4</v>
+        <v>12.47</v>
       </c>
       <c r="C28" s="3" t="n">
         <v>6.99</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>4.7</v>
+        <v>4.67</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>3.19</v>
+        <v>3.16</v>
       </c>
       <c r="F28" s="3" t="n">
         <v>0.4</v>
@@ -1441,13 +1441,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>29.81</v>
+        <v>29.94</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>15.56</v>
+        <v>15.62</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>11.26</v>
+        <v>11.29</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>3.43</v>
@@ -1475,16 +1475,16 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>45.38</v>
+        <v>45.35</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>21.39</v>
+        <v>21.28</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>12.74</v>
+        <v>12.67</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>6.25</v>
+        <v>6.18</v>
       </c>
       <c r="F30" s="3" t="n">
         <v>0.38</v>
@@ -1509,13 +1509,13 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>55.81</v>
+        <v>55.95</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>25.74</v>
+        <v>25.81</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>19.15</v>
+        <v>19.25</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>7.06</v>
@@ -1543,7 +1543,7 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>13.78</v>
+        <v>13.68</v>
       </c>
       <c r="C32" s="3" t="n">
         <v>4.97</v>
@@ -1552,7 +1552,7 @@
         <v>3.89</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="F32" s="3" t="n">
         <v>1.15</v>
@@ -1583,7 +1583,7 @@
         <v>4.1</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>2.89</v>
+        <v>2.92</v>
       </c>
       <c r="E33" s="3" t="n">
         <v>0.37</v>
@@ -1611,16 +1611,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>3.76</v>
+        <v>3.83</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>2.86</v>
+        <v>2.89</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="F34" s="3" t="n">
         <v>0.37</v>
@@ -1657,7 +1657,7 @@
         <v>2.64</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>0.82</v>
+        <v>0.74</v>
       </c>
       <c r="G35" s="3" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>3.8</v>
+        <v>3.73</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>2.86</v>
@@ -1951,13 +1951,13 @@
         </is>
       </c>
       <c r="B44" s="3" t="n">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="C44" s="3" t="n">
-        <v>7.57</v>
+        <v>7.47</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>6.08</v>
+        <v>6.01</v>
       </c>
       <c r="E44" s="3" t="n">
         <v>4.97</v>
@@ -2090,13 +2090,13 @@
         <v>6.85</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>5.44</v>
+        <v>5.41</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>5.07</v>
+        <v>5.04</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>4.84</v>
+        <v>4.81</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>4.47</v>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="B50" s="3" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.97</v>
       </c>
       <c r="C50" s="3" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="D50" s="3" t="n">
         <v>0.34</v>
@@ -2189,7 +2189,7 @@
         </is>
       </c>
       <c r="B51" s="3" t="n">
-        <v>13.89</v>
+        <v>13.85</v>
       </c>
       <c r="C51" s="3" t="n">
         <v>7.88</v>
@@ -2223,16 +2223,16 @@
         </is>
       </c>
       <c r="B52" s="3" t="n">
-        <v>30.48</v>
+        <v>30.38</v>
       </c>
       <c r="C52" s="3" t="n">
-        <v>20.83</v>
+        <v>20.87</v>
       </c>
       <c r="D52" s="3" t="n">
-        <v>9.710000000000001</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>8.17</v>
+        <v>8.23</v>
       </c>
       <c r="F52" s="3" t="n">
         <v>1.01</v>
@@ -2257,7 +2257,7 @@
         </is>
       </c>
       <c r="B53" s="3" t="n">
-        <v>19.46</v>
+        <v>19.56</v>
       </c>
       <c r="C53" s="3" t="n">
         <v>9.949999999999999</v>
@@ -2291,19 +2291,19 @@
         </is>
       </c>
       <c r="B54" s="3" t="n">
-        <v>21.67</v>
+        <v>21.77</v>
       </c>
       <c r="C54" s="3" t="n">
-        <v>12.67</v>
+        <v>12.64</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>11.74</v>
+        <v>11.7</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>11.15</v>
+        <v>11.11</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>9.41</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="G54" s="3" t="n">
         <v>0.31</v>
@@ -2325,19 +2325,19 @@
         </is>
       </c>
       <c r="B55" s="3" t="n">
-        <v>8.23</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="C55" s="3" t="n">
-        <v>6.38</v>
+        <v>6.35</v>
       </c>
       <c r="D55" s="3" t="n">
-        <v>5.44</v>
+        <v>5.41</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>4.77</v>
+        <v>4.74</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>3.33</v>
+        <v>3.29</v>
       </c>
       <c r="G55" s="3" t="n">
         <v>0.2</v>
@@ -2393,19 +2393,19 @@
         </is>
       </c>
       <c r="B57" s="3" t="n">
-        <v>8</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="C57" s="3" t="n">
-        <v>7.66</v>
+        <v>7.69</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>6.96</v>
+        <v>6.99</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>6.72</v>
+        <v>6.75</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>5.31</v>
+        <v>5.34</v>
       </c>
       <c r="G57" s="3" t="n">
         <v>0.07000000000000001</v>
@@ -2461,19 +2461,19 @@
         </is>
       </c>
       <c r="B59" s="3" t="n">
-        <v>9.34</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="C59" s="3" t="n">
-        <v>8.48</v>
+        <v>8.51</v>
       </c>
       <c r="D59" s="3" t="n">
-        <v>7.94</v>
+        <v>7.97</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>7.51</v>
+        <v>7.54</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>5.85</v>
+        <v>5.89</v>
       </c>
       <c r="G59" s="3" t="n">
         <v>0.5</v>
@@ -2495,19 +2495,19 @@
         </is>
       </c>
       <c r="B60" s="3" t="n">
-        <v>4</v>
+        <v>3.97</v>
       </c>
       <c r="C60" s="3" t="n">
-        <v>3.73</v>
+        <v>3.7</v>
       </c>
       <c r="D60" s="3" t="n">
-        <v>3.63</v>
+        <v>3.6</v>
       </c>
       <c r="E60" s="3" t="n">
-        <v>3.39</v>
+        <v>3.36</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="G60" s="3" t="n">
         <v>0</v>
@@ -2665,7 +2665,7 @@
         </is>
       </c>
       <c r="B65" s="3" t="n">
-        <v>4.84</v>
+        <v>4.87</v>
       </c>
       <c r="C65" s="3" t="n">
         <v>3.23</v>
@@ -2699,19 +2699,19 @@
         </is>
       </c>
       <c r="B66" s="3" t="n">
-        <v>50.31</v>
+        <v>50.28</v>
       </c>
       <c r="C66" s="3" t="n">
-        <v>6.91</v>
+        <v>6.84</v>
       </c>
       <c r="D66" s="3" t="n">
-        <v>6.22</v>
+        <v>6.18</v>
       </c>
       <c r="E66" s="3" t="n">
         <v>5.28</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>4.27</v>
+        <v>4.31</v>
       </c>
       <c r="G66" s="3" t="n">
         <v>0.03</v>
@@ -2733,10 +2733,10 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>18.55</v>
+        <v>18.45</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>2.28</v>
@@ -2767,19 +2767,19 @@
         </is>
       </c>
       <c r="B68" s="3" t="n">
-        <v>9.029999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="C68" s="3" t="n">
-        <v>8.890000000000001</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>8.58</v>
+        <v>8.65</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>8.06</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>6.63</v>
+        <v>6.67</v>
       </c>
       <c r="G68" s="3" t="n">
         <v>0.31</v>
@@ -2801,16 +2801,16 @@
         </is>
       </c>
       <c r="B69" s="3" t="n">
-        <v>24.66</v>
+        <v>24.6</v>
       </c>
       <c r="C69" s="3" t="n">
-        <v>23.42</v>
+        <v>23.35</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>22.14</v>
+        <v>22.08</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>16.13</v>
+        <v>16.1</v>
       </c>
       <c r="F69" s="3" t="n">
         <v>1.41</v>
@@ -2835,22 +2835,22 @@
         </is>
       </c>
       <c r="B70" s="3" t="n">
-        <v>7.8</v>
+        <v>7.76</v>
       </c>
       <c r="C70" s="3" t="n">
-        <v>7.8</v>
+        <v>7.76</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>7.39</v>
+        <v>7.36</v>
       </c>
       <c r="E70" s="3" t="n">
         <v>7.16</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>5.75</v>
+        <v>5.81</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>4.3</v>
+        <v>4.37</v>
       </c>
       <c r="H70" s="3" t="n">
         <v>0</v>
@@ -2869,19 +2869,19 @@
         </is>
       </c>
       <c r="B71" s="3" t="n">
-        <v>2.83</v>
+        <v>2.86</v>
       </c>
       <c r="C71" s="3" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="G71" s="3" t="n">
         <v>0.93</v>
@@ -3107,7 +3107,7 @@
         </is>
       </c>
       <c r="B78" s="3" t="n">
-        <v>20.66</v>
+        <v>20.62</v>
       </c>
       <c r="C78" s="3" t="n">
         <v>0.97</v>
@@ -3141,7 +3141,7 @@
         </is>
       </c>
       <c r="B79" s="3" t="n">
-        <v>19.46</v>
+        <v>19.42</v>
       </c>
       <c r="C79" s="3" t="n">
         <v>1.61</v>
@@ -3175,7 +3175,7 @@
         </is>
       </c>
       <c r="B80" s="3" t="n">
-        <v>5.76</v>
+        <v>5.73</v>
       </c>
       <c r="C80" s="3" t="n">
         <v>1.74</v>
@@ -3447,7 +3447,7 @@
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>6.59</v>
+        <v>6.52</v>
       </c>
       <c r="C88" s="3" t="n">
         <v>0.27</v>
@@ -3593,7 +3593,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>0</v>
@@ -3831,25 +3831,25 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>4.64</v>
+        <v>4.5</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.97</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>0.84</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="I9" s="3" t="n">
         <v>0.03</v>
@@ -3865,31 +3865,31 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.87</v>
+        <v>0.91</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.84</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.74</v>
+        <v>0.77</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.74</v>
+        <v>0.77</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.17</v>
+        <v>0.2</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.17</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="11">
@@ -3933,7 +3933,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>0.6</v>
@@ -4001,25 +4001,25 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>6.75</v>
+        <v>6.38</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.2</v>
+        <v>0.24</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.13</v>
+        <v>0.17</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>0</v>
@@ -4069,7 +4069,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.67</v>
+        <v>0.47</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>0.2</v>
@@ -4171,16 +4171,16 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>8.17</v>
+        <v>8.06</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>4.17</v>
+        <v>4.13</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>3.63</v>
+        <v>3.6</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="F19" s="3" t="n">
         <v>2.35</v>
@@ -4239,16 +4239,16 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>7.49</v>
+        <v>7.33</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>5.01</v>
+        <v>5.04</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>4.91</v>
+        <v>4.94</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>4.54</v>
+        <v>4.57</v>
       </c>
       <c r="F21" s="3" t="n">
         <v>2.62</v>
@@ -4375,7 +4375,7 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>6.01</v>
+        <v>5.94</v>
       </c>
       <c r="C25" s="3" t="n">
         <v>0.9</v>
@@ -4409,7 +4409,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="C26" s="3" t="n">
         <v>0.3</v>
@@ -4443,16 +4443,16 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>2.71</v>
+        <v>2.67</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>0.17</v>
@@ -4477,16 +4477,16 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>12.4</v>
+        <v>12.47</v>
       </c>
       <c r="C28" s="3" t="n">
         <v>6.99</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>4.7</v>
+        <v>4.67</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>3.19</v>
+        <v>3.16</v>
       </c>
       <c r="F28" s="3" t="n">
         <v>0.4</v>
@@ -4511,13 +4511,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>29.81</v>
+        <v>29.94</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>15.56</v>
+        <v>15.62</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>11.26</v>
+        <v>11.29</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>3.43</v>
@@ -4545,16 +4545,16 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>45.38</v>
+        <v>45.35</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>21.39</v>
+        <v>21.28</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>12.74</v>
+        <v>12.67</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>6.25</v>
+        <v>6.18</v>
       </c>
       <c r="F30" s="3" t="n">
         <v>0.38</v>
@@ -4579,13 +4579,13 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>55.81</v>
+        <v>55.95</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>25.74</v>
+        <v>25.81</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>19.15</v>
+        <v>19.25</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>7.06</v>
@@ -4613,7 +4613,7 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>13.78</v>
+        <v>13.68</v>
       </c>
       <c r="C32" s="3" t="n">
         <v>4.97</v>
@@ -4622,7 +4622,7 @@
         <v>3.89</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="F32" s="3" t="n">
         <v>1.15</v>
@@ -4653,7 +4653,7 @@
         <v>4.1</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>2.89</v>
+        <v>2.92</v>
       </c>
       <c r="E33" s="3" t="n">
         <v>0.37</v>
@@ -4681,16 +4681,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>3.76</v>
+        <v>3.83</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>2.86</v>
+        <v>2.89</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="F34" s="3" t="n">
         <v>0.37</v>
@@ -4727,7 +4727,7 @@
         <v>2.64</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>0.82</v>
+        <v>0.74</v>
       </c>
       <c r="G35" s="3" t="n">
         <v>0</v>
@@ -4749,7 +4749,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>3.8</v>
+        <v>3.73</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>2.86</v>
@@ -5021,13 +5021,13 @@
         </is>
       </c>
       <c r="B44" s="3" t="n">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="C44" s="3" t="n">
-        <v>7.57</v>
+        <v>7.47</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>6.08</v>
+        <v>6.01</v>
       </c>
       <c r="E44" s="3" t="n">
         <v>4.97</v>
@@ -5160,13 +5160,13 @@
         <v>6.85</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>5.44</v>
+        <v>5.41</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>5.07</v>
+        <v>5.04</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>4.84</v>
+        <v>4.81</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>4.47</v>
@@ -5225,10 +5225,10 @@
         </is>
       </c>
       <c r="B50" s="3" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.97</v>
       </c>
       <c r="C50" s="3" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="D50" s="3" t="n">
         <v>0.34</v>
@@ -5259,7 +5259,7 @@
         </is>
       </c>
       <c r="B51" s="3" t="n">
-        <v>13.89</v>
+        <v>13.85</v>
       </c>
       <c r="C51" s="3" t="n">
         <v>7.88</v>
@@ -5293,16 +5293,16 @@
         </is>
       </c>
       <c r="B52" s="3" t="n">
-        <v>30.48</v>
+        <v>30.38</v>
       </c>
       <c r="C52" s="3" t="n">
-        <v>20.83</v>
+        <v>20.87</v>
       </c>
       <c r="D52" s="3" t="n">
-        <v>9.710000000000001</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>8.17</v>
+        <v>8.23</v>
       </c>
       <c r="F52" s="3" t="n">
         <v>1.01</v>
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="B53" s="3" t="n">
-        <v>19.46</v>
+        <v>19.56</v>
       </c>
       <c r="C53" s="3" t="n">
         <v>9.949999999999999</v>
@@ -5361,19 +5361,19 @@
         </is>
       </c>
       <c r="B54" s="3" t="n">
-        <v>21.67</v>
+        <v>21.77</v>
       </c>
       <c r="C54" s="3" t="n">
-        <v>12.67</v>
+        <v>12.64</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>11.74</v>
+        <v>11.7</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>11.15</v>
+        <v>11.11</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>9.41</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="G54" s="3" t="n">
         <v>0.31</v>
@@ -5395,19 +5395,19 @@
         </is>
       </c>
       <c r="B55" s="3" t="n">
-        <v>8.23</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="C55" s="3" t="n">
-        <v>6.38</v>
+        <v>6.35</v>
       </c>
       <c r="D55" s="3" t="n">
-        <v>5.44</v>
+        <v>5.41</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>4.77</v>
+        <v>4.74</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>3.33</v>
+        <v>3.29</v>
       </c>
       <c r="G55" s="3" t="n">
         <v>0.2</v>
@@ -5463,19 +5463,19 @@
         </is>
       </c>
       <c r="B57" s="3" t="n">
-        <v>8</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="C57" s="3" t="n">
-        <v>7.66</v>
+        <v>7.69</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>6.96</v>
+        <v>6.99</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>6.72</v>
+        <v>6.75</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>5.31</v>
+        <v>5.34</v>
       </c>
       <c r="G57" s="3" t="n">
         <v>0.07000000000000001</v>
@@ -5531,19 +5531,19 @@
         </is>
       </c>
       <c r="B59" s="3" t="n">
-        <v>9.34</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="C59" s="3" t="n">
-        <v>8.48</v>
+        <v>8.51</v>
       </c>
       <c r="D59" s="3" t="n">
-        <v>7.94</v>
+        <v>7.97</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>7.51</v>
+        <v>7.54</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>5.85</v>
+        <v>5.89</v>
       </c>
       <c r="G59" s="3" t="n">
         <v>0.5</v>
@@ -5565,19 +5565,19 @@
         </is>
       </c>
       <c r="B60" s="3" t="n">
-        <v>4</v>
+        <v>3.97</v>
       </c>
       <c r="C60" s="3" t="n">
-        <v>3.73</v>
+        <v>3.7</v>
       </c>
       <c r="D60" s="3" t="n">
-        <v>3.63</v>
+        <v>3.6</v>
       </c>
       <c r="E60" s="3" t="n">
-        <v>3.39</v>
+        <v>3.36</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="G60" s="3" t="n">
         <v>0</v>
@@ -5735,7 +5735,7 @@
         </is>
       </c>
       <c r="B65" s="3" t="n">
-        <v>4.84</v>
+        <v>4.87</v>
       </c>
       <c r="C65" s="3" t="n">
         <v>3.23</v>
@@ -5769,19 +5769,19 @@
         </is>
       </c>
       <c r="B66" s="3" t="n">
-        <v>50.31</v>
+        <v>50.28</v>
       </c>
       <c r="C66" s="3" t="n">
-        <v>6.91</v>
+        <v>6.84</v>
       </c>
       <c r="D66" s="3" t="n">
-        <v>6.22</v>
+        <v>6.18</v>
       </c>
       <c r="E66" s="3" t="n">
         <v>5.28</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>4.27</v>
+        <v>4.31</v>
       </c>
       <c r="G66" s="3" t="n">
         <v>0.03</v>
@@ -5803,10 +5803,10 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>18.55</v>
+        <v>18.45</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>2.28</v>
@@ -5837,19 +5837,19 @@
         </is>
       </c>
       <c r="B68" s="3" t="n">
-        <v>9.029999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="C68" s="3" t="n">
-        <v>8.890000000000001</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>8.58</v>
+        <v>8.65</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>8.06</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>6.63</v>
+        <v>6.67</v>
       </c>
       <c r="G68" s="3" t="n">
         <v>0.31</v>
@@ -5871,16 +5871,16 @@
         </is>
       </c>
       <c r="B69" s="3" t="n">
-        <v>24.66</v>
+        <v>24.6</v>
       </c>
       <c r="C69" s="3" t="n">
-        <v>23.42</v>
+        <v>23.35</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>22.14</v>
+        <v>22.08</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>16.13</v>
+        <v>16.1</v>
       </c>
       <c r="F69" s="3" t="n">
         <v>1.41</v>
@@ -5905,22 +5905,22 @@
         </is>
       </c>
       <c r="B70" s="3" t="n">
-        <v>7.8</v>
+        <v>7.76</v>
       </c>
       <c r="C70" s="3" t="n">
-        <v>7.8</v>
+        <v>7.76</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>7.39</v>
+        <v>7.36</v>
       </c>
       <c r="E70" s="3" t="n">
         <v>7.16</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>5.75</v>
+        <v>5.81</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>4.3</v>
+        <v>4.37</v>
       </c>
       <c r="H70" s="3" t="n">
         <v>0</v>
@@ -5939,19 +5939,19 @@
         </is>
       </c>
       <c r="B71" s="3" t="n">
-        <v>2.83</v>
+        <v>2.86</v>
       </c>
       <c r="C71" s="3" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="G71" s="3" t="n">
         <v>0.93</v>
@@ -6177,7 +6177,7 @@
         </is>
       </c>
       <c r="B78" s="3" t="n">
-        <v>20.66</v>
+        <v>20.62</v>
       </c>
       <c r="C78" s="3" t="n">
         <v>0.97</v>
@@ -6211,7 +6211,7 @@
         </is>
       </c>
       <c r="B79" s="3" t="n">
-        <v>19.46</v>
+        <v>19.42</v>
       </c>
       <c r="C79" s="3" t="n">
         <v>1.61</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="B80" s="3" t="n">
-        <v>5.76</v>
+        <v>5.73</v>
       </c>
       <c r="C80" s="3" t="n">
         <v>1.74</v>
@@ -6517,7 +6517,7 @@
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>6.59</v>
+        <v>6.52</v>
       </c>
       <c r="C88" s="3" t="n">
         <v>0.27</v>
@@ -6780,7 +6780,7 @@
         <v>2976</v>
       </c>
       <c r="C2" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" s="6" t="n">
         <v>0</v>
@@ -7039,25 +7039,25 @@
         <v>2976</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J9" s="6" t="n">
         <v>1</v>
@@ -7076,31 +7076,31 @@
         <v>2976</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
@@ -7150,7 +7150,7 @@
         <v>2976</v>
       </c>
       <c r="C12" s="6" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D12" s="6" t="n">
         <v>18</v>
@@ -7224,25 +7224,25 @@
         <v>2976</v>
       </c>
       <c r="C14" s="6" t="n">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" s="6" t="n">
         <v>0</v>
@@ -7298,7 +7298,7 @@
         <v>2976</v>
       </c>
       <c r="C16" s="6" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D16" s="6" t="n">
         <v>6</v>
@@ -7409,16 +7409,16 @@
         <v>2976</v>
       </c>
       <c r="C19" s="6" t="n">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G19" s="6" t="n">
         <v>70</v>
@@ -7483,16 +7483,16 @@
         <v>2976</v>
       </c>
       <c r="C21" s="6" t="n">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G21" s="6" t="n">
         <v>78</v>
@@ -7631,7 +7631,7 @@
         <v>2880</v>
       </c>
       <c r="C25" s="6" t="n">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D25" s="6" t="n">
         <v>26</v>
@@ -7668,7 +7668,7 @@
         <v>2976</v>
       </c>
       <c r="C26" s="6" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D26" s="6" t="n">
         <v>9</v>
@@ -7705,16 +7705,16 @@
         <v>2880</v>
       </c>
       <c r="C27" s="6" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G27" s="6" t="n">
         <v>5</v>
@@ -7742,16 +7742,16 @@
         <v>2976</v>
       </c>
       <c r="C28" s="6" t="n">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D28" s="6" t="n">
         <v>208</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G28" s="6" t="n">
         <v>12</v>
@@ -7779,13 +7779,13 @@
         <v>2976</v>
       </c>
       <c r="C29" s="6" t="n">
-        <v>887</v>
+        <v>891</v>
       </c>
       <c r="D29" s="6" t="n">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F29" s="6" t="n">
         <v>102</v>
@@ -7816,16 +7816,16 @@
         <v>2880</v>
       </c>
       <c r="C30" s="6" t="n">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="D30" s="6" t="n">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="G30" s="6" t="n">
         <v>11</v>
@@ -7853,13 +7853,13 @@
         <v>2976</v>
       </c>
       <c r="C31" s="6" t="n">
-        <v>1661</v>
+        <v>1665</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="F31" s="6" t="n">
         <v>210</v>
@@ -7890,7 +7890,7 @@
         <v>2880</v>
       </c>
       <c r="C32" s="6" t="n">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="D32" s="6" t="n">
         <v>143</v>
@@ -7899,7 +7899,7 @@
         <v>112</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G32" s="6" t="n">
         <v>33</v>
@@ -7933,7 +7933,7 @@
         <v>122</v>
       </c>
       <c r="E33" s="6" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F33" s="6" t="n">
         <v>11</v>
@@ -7964,16 +7964,16 @@
         <v>2976</v>
       </c>
       <c r="C34" s="6" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D34" s="6" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G34" s="6" t="n">
         <v>11</v>
@@ -8013,7 +8013,7 @@
         <v>71</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H35" s="6" t="n">
         <v>0</v>
@@ -8038,7 +8038,7 @@
         <v>2976</v>
       </c>
       <c r="C36" s="6" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D36" s="6" t="n">
         <v>85</v>
@@ -8334,13 +8334,13 @@
         <v>2880</v>
       </c>
       <c r="C44" s="6" t="n">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="D44" s="6" t="n">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="E44" s="6" t="n">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="F44" s="6" t="n">
         <v>143</v>
@@ -8485,13 +8485,13 @@
         <v>204</v>
       </c>
       <c r="D48" s="6" t="n">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E48" s="6" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F48" s="6" t="n">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G48" s="6" t="n">
         <v>133</v>
@@ -8556,10 +8556,10 @@
         <v>2976</v>
       </c>
       <c r="C50" s="6" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D50" s="6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E50" s="6" t="n">
         <v>10</v>
@@ -8593,7 +8593,7 @@
         <v>2880</v>
       </c>
       <c r="C51" s="6" t="n">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D51" s="6" t="n">
         <v>227</v>
@@ -8630,16 +8630,16 @@
         <v>2976</v>
       </c>
       <c r="C52" s="6" t="n">
-        <v>907</v>
+        <v>904</v>
       </c>
       <c r="D52" s="6" t="n">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="E52" s="6" t="n">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="F52" s="6" t="n">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="G52" s="6" t="n">
         <v>30</v>
@@ -8667,7 +8667,7 @@
         <v>2976</v>
       </c>
       <c r="C53" s="6" t="n">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="D53" s="6" t="n">
         <v>296</v>
@@ -8704,19 +8704,19 @@
         <v>2880</v>
       </c>
       <c r="C54" s="6" t="n">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="D54" s="6" t="n">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E54" s="6" t="n">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F54" s="6" t="n">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G54" s="6" t="n">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H54" s="6" t="n">
         <v>9</v>
@@ -8741,19 +8741,19 @@
         <v>2976</v>
       </c>
       <c r="C55" s="6" t="n">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D55" s="6" t="n">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E55" s="6" t="n">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G55" s="6" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H55" s="6" t="n">
         <v>6</v>
@@ -8815,19 +8815,19 @@
         <v>2976</v>
       </c>
       <c r="C57" s="6" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D57" s="6" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E57" s="6" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G57" s="6" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H57" s="6" t="n">
         <v>2</v>
@@ -8889,19 +8889,19 @@
         <v>2784</v>
       </c>
       <c r="C59" s="6" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D59" s="6" t="n">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E59" s="6" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G59" s="6" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H59" s="6" t="n">
         <v>14</v>
@@ -8926,19 +8926,19 @@
         <v>2976</v>
       </c>
       <c r="C60" s="6" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D60" s="6" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E60" s="6" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F60" s="6" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G60" s="6" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H60" s="6" t="n">
         <v>0</v>
@@ -9111,7 +9111,7 @@
         <v>2976</v>
       </c>
       <c r="C65" s="6" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D65" s="6" t="n">
         <v>96</v>
@@ -9148,19 +9148,19 @@
         <v>2880</v>
       </c>
       <c r="C66" s="6" t="n">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="D66" s="6" t="n">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E66" s="6" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F66" s="6" t="n">
         <v>152</v>
       </c>
       <c r="G66" s="6" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H66" s="6" t="n">
         <v>1</v>
@@ -9185,10 +9185,10 @@
         <v>2976</v>
       </c>
       <c r="C67" s="6" t="n">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="D67" s="6" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E67" s="6" t="n">
         <v>68</v>
@@ -9222,19 +9222,19 @@
         <v>2880</v>
       </c>
       <c r="C68" s="6" t="n">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="D68" s="6" t="n">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="E68" s="6" t="n">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F68" s="6" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="G68" s="6" t="n">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H68" s="6" t="n">
         <v>9</v>
@@ -9259,16 +9259,16 @@
         <v>2976</v>
       </c>
       <c r="C69" s="6" t="n">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="D69" s="6" t="n">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="E69" s="6" t="n">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="G69" s="6" t="n">
         <v>42</v>
@@ -9296,22 +9296,22 @@
         <v>2976</v>
       </c>
       <c r="C70" s="6" t="n">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D70" s="6" t="n">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E70" s="6" t="n">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F70" s="6" t="n">
         <v>213</v>
       </c>
       <c r="G70" s="6" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H70" s="6" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="I70" s="6" t="n">
         <v>0</v>
@@ -9333,19 +9333,19 @@
         <v>2688</v>
       </c>
       <c r="C71" s="6" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D71" s="6" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E71" s="6" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G71" s="6" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H71" s="6" t="n">
         <v>25</v>
@@ -9592,7 +9592,7 @@
         <v>2880</v>
       </c>
       <c r="C78" s="6" t="n">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="D78" s="6" t="n">
         <v>28</v>
@@ -9629,7 +9629,7 @@
         <v>2976</v>
       </c>
       <c r="C79" s="6" t="n">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="D79" s="6" t="n">
         <v>48</v>
@@ -9666,7 +9666,7 @@
         <v>2880</v>
       </c>
       <c r="C80" s="6" t="n">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D80" s="6" t="n">
         <v>50</v>
@@ -9962,7 +9962,7 @@
         <v>2976</v>
       </c>
       <c r="C88" s="6" t="n">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D88" s="6" t="n">
         <v>8</v>

--- a/outputs/TAS_negative_prices.xlsx
+++ b/outputs/TAS_negative_prices.xlsx
@@ -18,7 +18,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.00&quot;%&quot;"/>
+  </numFmts>
   <fonts count="3">
     <font>
       <name val="Calibri"/>
@@ -74,7 +76,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -6579,108 +6581,12 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B89">
+  <conditionalFormatting sqref="B2:J89">
     <cfRule type="colorScale" priority="1">
       <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C89">
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D89">
-    <cfRule type="colorScale" priority="3">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E89">
-    <cfRule type="colorScale" priority="4">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F89">
-    <cfRule type="colorScale" priority="5">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G89">
-    <cfRule type="colorScale" priority="6">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H89">
-    <cfRule type="colorScale" priority="7">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I89">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J89">
-    <cfRule type="colorScale" priority="9">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="10"/>
+        <cfvo type="num" val="50"/>
         <color rgb="0063BE7B"/>
         <color rgb="00FFEB84"/>
         <color rgb="00F8696B"/>
